--- a/Result/profitability/8047.xlsx
+++ b/Result/profitability/8047.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09375000000000003</v>
+        <v>-0.11875</v>
       </c>
       <c r="N2" t="n">
-        <v>34.33</v>
+        <v>35.0925</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05750000000000002</v>
+        <v>-0.03125000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>33.96375</v>
+        <v>35.05249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.001250000000000015</v>
+        <v>0.006249999999999985</v>
       </c>
       <c r="N4" t="n">
-        <v>33.47375</v>
+        <v>34.145</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01125000000000002</v>
+        <v>0.003749999999999986</v>
       </c>
       <c r="N5" t="n">
-        <v>32.3825</v>
+        <v>33.73999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06500000000000002</v>
+        <v>-0.03875000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>31.335</v>
+        <v>32.39375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09250000000000001</v>
+        <v>-0.03875000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>29.555</v>
+        <v>30.8825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.002500000000000023</v>
       </c>
       <c r="N8" t="n">
-        <v>29.04125</v>
+        <v>30.55125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8047</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>170</v>
+      </c>
+      <c r="D75" t="n">
+        <v>97</v>
+      </c>
+      <c r="E75" t="n">
+        <v>73</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.13125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.32375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.03448275862069</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3894261766602192</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.090909090909091</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3368486352357321</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
